--- a/content/tz-kurs-po-logistike-na-kitayskom.xlsx
+++ b/content/tz-kurs-po-logistike-na-kitayskom.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Курс по логистике на китайском: Инкотермс, документы поставки и что должно быть в программе</t>
+          <t>Курс по логистике на китайском языке: что нужно знать логисту и специалисту по ВЭД</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>38 725 знаков (лимит ≈ 50 000)</t>
+          <t>38 698 знаков (лимит ≈ 50 000)</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>38 725 знаков при лимите около 50 000</t>
+          <t>38 698 знаков при лимите около 50 000</t>
         </is>
       </c>
     </row>
